--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N79_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N79_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.46028369572485</v>
+        <v>2.187296100555288</v>
       </c>
       <c r="D2" t="n">
-        <v>3.835364176381809</v>
+        <v>0.6232466786620441</v>
       </c>
       <c r="E2" t="n">
-        <v>20.3774408609837</v>
+        <v>3.311334139909851</v>
       </c>
       <c r="F2" t="n">
-        <v>8.366151408850143</v>
+        <v>1.359499603938148</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.12142387048918</v>
+        <v>2.132231378954492</v>
       </c>
       <c r="D3" t="n">
-        <v>24.78655481257456</v>
+        <v>4.027815157043365</v>
       </c>
       <c r="E3" t="n">
-        <v>20.3774408609837</v>
+        <v>3.311334139909851</v>
       </c>
       <c r="F3" t="n">
-        <v>8.366151408850143</v>
+        <v>1.359499603938148</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.33477469258919</v>
+        <v>8.504400887545744</v>
       </c>
       <c r="D4" t="n">
-        <v>8.467452577653855</v>
+        <v>1.375961043868752</v>
       </c>
       <c r="E4" t="n">
-        <v>20.3774408609837</v>
+        <v>3.311334139909851</v>
       </c>
       <c r="F4" t="n">
-        <v>8.366151408850143</v>
+        <v>1.359499603938148</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.62256073937476</v>
+        <v>9.038666120148399</v>
       </c>
       <c r="D5" t="n">
-        <v>5.270462766947298</v>
+        <v>0.856450199628936</v>
       </c>
       <c r="E5" t="n">
-        <v>20.3774408609837</v>
+        <v>3.311334139909851</v>
       </c>
       <c r="F5" t="n">
-        <v>8.366151408850143</v>
+        <v>1.359499603938148</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
